--- a/batches/2026-09-17_0421ET_fix_delivery_rollforward/lng_carrier_fix.xlsx
+++ b/batches/2026-09-17_0421ET_fix_delivery_rollforward/lng_carrier_fix.xlsx
@@ -494,14 +494,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Delivery roll-forward - on-order rows checked against shipvault + vesselfinder (2026-09-17)</t>
+          <t>Delivery roll-forward - on-order rows checked against shipvault + vesselfinder + marinetraffic.org (2026-09-17)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Backend had not moved since June 2026. Every on-order row with an IMO was looked up in shipvault (status / delivered date / yard no.) and vesselfinder (AIS-registered name, MMSI, year built). Delivered vessels move to active with their real name; delivery years are corrected to the actual year; undelivered 2026 rows that shipvault now schedules for 2027+ are rolled forward.</t>
+          <t>Backend had not moved since June 2026. Every on-order row with an IMO was looked up in shipvault (status / delivered date / yard no.) and vesselfinder (AIS-registered name, MMSI, year built). Delivered vessels move to active with their real name; delivery years are corrected to the actual year; undelivered 2026 rows that shipvault now schedules for 2027+ are rolled forward. The rows vesselfinder never answered (IP ban at ~150/323) were cross-checked on marinetraffic.org the same afternoon (95 IMOs, paced).</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rows corrected: 141   Refs checked: 426   Refs dropped/removed: 0</t>
+          <t>Rows corrected: 150   Refs checked: 454   Refs dropped/removed: 0</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT142"/>
+  <dimension ref="A1:AT151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18405,14 +18405,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>Al Ghuwair</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478305, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478305</t>
+          <t>https://www.shipvault.com/ships/478305, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478305, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-GHUWAIR/1048918/538000000</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -18573,14 +18573,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Wadi Sultana</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478306, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306</t>
+          <t>https://www.shipvault.com/ships/478306, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306, https://www.marinetraffic.org/ship-owner-manager-ism-data/WADI-SULTANA/1048920/1</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
@@ -18741,14 +18741,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D106" s="7" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Lesha</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478307, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307</t>
+          <t>https://www.shipvault.com/ships/478307, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307, https://www.marinetraffic.org/ship-owner-manager-ism-data/LESHA/1048932/1</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
@@ -18909,14 +18909,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D107" s="7" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>Al Jazi</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478308, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308</t>
+          <t>https://www.shipvault.com/ships/478308, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-JAZI/1048944/1</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
@@ -19077,14 +19077,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>Al Mashrab</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478309, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309</t>
+          <t>https://www.shipvault.com/ships/478309, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-MASHRAB/1048956/1</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
@@ -19245,14 +19245,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Al Mirzam</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478310, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310</t>
+          <t>https://www.shipvault.com/ships/478310, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-MIRZAM/1048982/1</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
@@ -19413,14 +19413,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D110" s="7" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>Maqdeem</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478311, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311</t>
+          <t>https://www.shipvault.com/ships/478311, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311, https://www.marinetraffic.org/ship-owner-manager-ism-data/MAQDEEM/1048994/1</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
@@ -19581,14 +19581,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>Al Rufaa</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478312, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312</t>
+          <t>https://www.shipvault.com/ships/478312, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-RUFAA/1049003/1</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
@@ -19749,14 +19749,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D112" s="7" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Al Nekhsh</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478313, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313</t>
+          <t>https://www.shipvault.com/ships/478313, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NEKHSH/1049015/1</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -19917,14 +19917,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D113" s="7" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Leh'saien</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478314, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314</t>
+          <t>https://www.shipvault.com/ships/478314, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314, https://www.marinetraffic.org/ship-owner-manager-ism-data/LEH'SAIEN/1049027/1</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
@@ -20085,14 +20085,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>Le'shara</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478315, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315</t>
+          <t>https://www.shipvault.com/ships/478315, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315, https://www.marinetraffic.org/ship-owner-manager-ism-data/LE'SHARA/1049039/1</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
@@ -20253,14 +20253,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Librega</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478316, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316</t>
+          <t>https://www.shipvault.com/ships/478316, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316, https://www.marinetraffic.org/ship-owner-manager-ism-data/LIBREGA/1049041/1</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
@@ -20421,14 +20421,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D116" s="7" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Eshairej</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478317, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317</t>
+          <t>https://www.shipvault.com/ships/478317, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317, https://www.marinetraffic.org/ship-owner-manager-ism-data/ESHAIREJ/1049053/1</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
@@ -20589,14 +20589,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>Mneefa</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478318, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318</t>
+          <t>https://www.shipvault.com/ships/478318, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318, https://www.marinetraffic.org/ship-owner-manager-ism-data/MNEEFA/1049065/1</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
@@ -20757,14 +20757,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D118" s="7" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Ezhara</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478319, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319</t>
+          <t>https://www.shipvault.com/ships/478319, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319, https://www.marinetraffic.org/ship-owner-manager-ism-data/EZHARA/1049089/1</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
@@ -20912,12 +20912,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>9986570</t>
+          <t>1023877</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -20927,12 +20927,12 @@
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Al Sabsab</t>
+          <t>Diamond Gas Nexus</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462933, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/DIAMOND-GAS-NEXUS/1023877/563334400</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
@@ -20940,7 +20940,7 @@
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>Hull H1794A</t>
+          <t>Hull 8208 (HSHI)</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -20970,7 +20970,7 @@
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>MOL, COSCO</t>
+          <t>NYK Line</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
@@ -20982,7 +20982,7 @@
       <c r="R119" s="2" t="inlineStr"/>
       <c r="S119" s="4" t="inlineStr">
         <is>
-          <t>Hudong-Zhonghua Shipbuilding</t>
+          <t>HD Hyundai Samho</t>
         </is>
       </c>
       <c r="T119" s="4" t="inlineStr">
@@ -20992,27 +20992,27 @@
       </c>
       <c r="U119" s="4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="V119" s="4" t="inlineStr">
         <is>
-          <t>https://www.shipyards.gr/shipyards/new-buildings-shipyards/newbuilding-farest-pacific-ocean/newbuilding-far-east-china-sea/china-south/hudong-zhonghua-shipbuilding-group-coltd</t>
+          <t>https://www.hshi.co.kr/eng/</t>
         </is>
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>31.271988</t>
+          <t>34.75031</t>
         </is>
       </c>
       <c r="X119" s="4" t="inlineStr">
         <is>
-          <t>121.575478</t>
+          <t>126.3875</t>
         </is>
       </c>
       <c r="Y119" s="4" t="inlineStr">
         <is>
-          <t>7HCG+R4 Pudong, Shanghai, China</t>
+          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
         </is>
       </c>
       <c r="Z119" s="4" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="AA119" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hudong-Zhonghua+Shipbuilding/@31.2720706,121.5727207,753m/data=!3m2!1e3!4b1!4m6!3m5!1s0x35b2742eceeb203d:0x37fddc7176d2cc24!8m2!3d31.2720706!4d121.5752956!16s%2Fg%2F1td0qx6d?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB119" s="4" t="inlineStr">
@@ -21080,12 +21080,12 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>9994034</t>
+          <t>1023889</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -21093,24 +21093,32 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>Clean Rio Grande</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Grace Himawari</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/GRACE-HIMAWARI/1023889/1</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
       <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-      <c r="K120" s="7" t="inlineStr">
-        <is>
-          <t>active</t>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>Hull 8209 (HSHI)</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
@@ -21123,14 +21131,14 @@
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="N120" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/466740, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>Dynagas</t>
+          <t>NYK Line</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
@@ -21142,7 +21150,7 @@
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Heavy Industries</t>
+          <t>HD Hyundai Samho</t>
         </is>
       </c>
       <c r="T120" s="4" t="inlineStr">
@@ -21157,22 +21165,22 @@
       </c>
       <c r="V120" s="4" t="inlineStr">
         <is>
-          <t>https://www.hd.com/en/main</t>
+          <t>https://www.hshi.co.kr/eng/</t>
         </is>
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>35.51613</t>
+          <t>34.75031</t>
         </is>
       </c>
       <c r="X120" s="4" t="inlineStr">
         <is>
-          <t>129.4383</t>
+          <t>126.3875</t>
         </is>
       </c>
       <c r="Y120" s="4" t="inlineStr">
         <is>
-          <t>GC8Q+M6 Ulsan</t>
+          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
         </is>
       </c>
       <c r="Z120" s="4" t="inlineStr">
@@ -21182,12 +21190,12 @@
       </c>
       <c r="AA120" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB120" s="4" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="AC120" s="4" t="inlineStr">
@@ -21206,7 +21214,7 @@
       <c r="AH120" s="2" t="inlineStr"/>
       <c r="AI120" s="4" t="inlineStr">
         <is>
-          <t>ME-GA</t>
+          <t>X-DF</t>
         </is>
       </c>
       <c r="AJ120" s="4" t="inlineStr">
@@ -21214,14 +21222,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK120" s="7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AL120" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/466740, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
+      <c r="AK120" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="AL120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="AM120" s="4" t="inlineStr">
@@ -21240,12 +21248,12 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>9994008</t>
+          <t>1023906</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -21253,24 +21261,36 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Clean Texas</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr"/>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Grace Gerbera</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/GRACE-GERBERA/1023906/1</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>2027 delivery date seems to be confirmed, but was originally 2025 in IGU</t>
+        </is>
+      </c>
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-      <c r="K121" s="7" t="inlineStr">
-        <is>
-          <t>active</t>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>Hull 8238 (HSHI)</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
         </is>
       </c>
       <c r="L121" s="4" t="inlineStr">
@@ -21280,17 +21300,17 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
-        </is>
-      </c>
-      <c r="N121" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/466739, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
+          <t>12/18/2025</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>http://www.chinashipbuilding.cn/ship.aspx?pklujyukkpp4SFBBcanmkhTk8Pl4EN</t>
         </is>
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>Dynagas</t>
+          <t>NYK Line</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
@@ -21302,7 +21322,7 @@
       <c r="R121" s="2" t="inlineStr"/>
       <c r="S121" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Heavy Industries</t>
+          <t>HD Hyundai Samho</t>
         </is>
       </c>
       <c r="T121" s="4" t="inlineStr">
@@ -21317,22 +21337,22 @@
       </c>
       <c r="V121" s="4" t="inlineStr">
         <is>
-          <t>https://www.hd.com/en/main</t>
+          <t>https://www.hshi.co.kr/eng/</t>
         </is>
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>35.51613</t>
+          <t>34.75031</t>
         </is>
       </c>
       <c r="X121" s="4" t="inlineStr">
         <is>
-          <t>129.4383</t>
+          <t>126.3875</t>
         </is>
       </c>
       <c r="Y121" s="4" t="inlineStr">
         <is>
-          <t>GC8Q+M6 Ulsan</t>
+          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
         </is>
       </c>
       <c r="Z121" s="4" t="inlineStr">
@@ -21342,12 +21362,12 @@
       </c>
       <c r="AA121" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB121" s="4" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="AC121" s="4" t="inlineStr">
@@ -21366,7 +21386,7 @@
       <c r="AH121" s="2" t="inlineStr"/>
       <c r="AI121" s="4" t="inlineStr">
         <is>
-          <t>ME-GA</t>
+          <t>X-DF</t>
         </is>
       </c>
       <c r="AJ121" s="4" t="inlineStr">
@@ -21374,14 +21394,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK121" s="7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AL121" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/466739, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
+      <c r="AK121" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="AL121" s="4" t="inlineStr">
+        <is>
+          <t>http://www.chinashipbuilding.cn/ship.aspx?pklujyukkpp4SFBBcanmkhTk8Pl4EN, https://www.marinelink.com/news/maritime/hyundai-samho-heavy-industries</t>
         </is>
       </c>
       <c r="AM121" s="4" t="inlineStr">
@@ -21400,12 +21420,12 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>1030569</t>
+          <t>1023918</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -21415,19 +21435,27 @@
       </c>
       <c r="D122" s="7" t="inlineStr">
         <is>
-          <t>Alliance Venture</t>
+          <t>Ferdy Vanguard</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469428, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469428</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/FERDY-VANGUARD/1023918/1</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr"/>
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>Hull 8239 (HSHI)</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -21440,17 +21468,17 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>12/31/2024</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="N122" s="4" t="inlineStr">
         <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+          <t>http://www.chinashipbuilding.cn/shipyard.aspx?pklujyukkpp4BbccCanmkhTk8Pl4ENaORDERBOOK4c</t>
         </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>Wah Kwong, China Gas, CSSC</t>
+          <t>NYK Line</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
@@ -21462,7 +21490,7 @@
       <c r="R122" s="2" t="inlineStr"/>
       <c r="S122" s="4" t="inlineStr">
         <is>
-          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+          <t>HD Hyundai Samho</t>
         </is>
       </c>
       <c r="T122" s="4" t="inlineStr">
@@ -21472,27 +21500,27 @@
       </c>
       <c r="U122" s="4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="V122" s="4" t="inlineStr">
         <is>
-          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+          <t>https://www.hshi.co.kr/eng/</t>
         </is>
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>38.937861</t>
+          <t>34.75031</t>
         </is>
       </c>
       <c r="X122" s="4" t="inlineStr">
         <is>
-          <t>121.638613</t>
+          <t>126.3875</t>
         </is>
       </c>
       <c r="Y122" s="4" t="inlineStr">
         <is>
-          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
         </is>
       </c>
       <c r="Z122" s="4" t="inlineStr">
@@ -21502,12 +21530,12 @@
       </c>
       <c r="AA122" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB122" s="4" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="AC122" s="4" t="inlineStr">
@@ -21541,7 +21569,7 @@
       </c>
       <c r="AL122" s="4" t="inlineStr">
         <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+          <t>http://www.chinashipbuilding.cn/shipyard.aspx?pklujyukkpp4BbccCanmkhTk8Pl4ENaORDERBOOK4c</t>
         </is>
       </c>
       <c r="AM122" s="4" t="inlineStr">
@@ -21560,12 +21588,12 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>9980552</t>
+          <t>9986570</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -21573,24 +21601,32 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
-        <is>
-          <t>Elisa Halcyon</t>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Al Sabsab</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+          <t>https://www.shipvault.com/ships/462933, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SABSAB/9986570/636025823</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr"/>
       <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr">
-        <is>
-          <t>active</t>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>Hull H1794A</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
         </is>
       </c>
       <c r="L123" s="4" t="inlineStr">
@@ -21603,14 +21639,14 @@
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="N123" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>NYK Line</t>
+          <t>MOL, COSCO</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
@@ -21622,7 +21658,7 @@
       <c r="R123" s="2" t="inlineStr"/>
       <c r="S123" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Samho</t>
+          <t>Hudong-Zhonghua Shipbuilding</t>
         </is>
       </c>
       <c r="T123" s="4" t="inlineStr">
@@ -21632,27 +21668,27 @@
       </c>
       <c r="U123" s="4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="V123" s="4" t="inlineStr">
         <is>
-          <t>https://www.hshi.co.kr/eng/</t>
+          <t>https://www.shipyards.gr/shipyards/new-buildings-shipyards/newbuilding-farest-pacific-ocean/newbuilding-far-east-china-sea/china-south/hudong-zhonghua-shipbuilding-group-coltd</t>
         </is>
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>34.75031</t>
+          <t>31.271988</t>
         </is>
       </c>
       <c r="X123" s="4" t="inlineStr">
         <is>
-          <t>126.3875</t>
+          <t>121.575478</t>
         </is>
       </c>
       <c r="Y123" s="4" t="inlineStr">
         <is>
-          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
+          <t>7HCG+R4 Pudong, Shanghai, China</t>
         </is>
       </c>
       <c r="Z123" s="4" t="inlineStr">
@@ -21662,7 +21698,7 @@
       </c>
       <c r="AA123" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hudong-Zhonghua+Shipbuilding/@31.2720706,121.5727207,753m/data=!3m2!1e3!4b1!4m6!3m5!1s0x35b2742eceeb203d:0x37fddc7176d2cc24!8m2!3d31.2720706!4d121.5752956!16s%2Fg%2F1td0qx6d?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB123" s="4" t="inlineStr">
@@ -21694,14 +21730,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK123" s="7" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AL123" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+      <c r="AK123" s="4" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="AL123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="AM123" s="4" t="inlineStr">
@@ -21720,12 +21756,12 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>1069821</t>
+          <t>9986582</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -21735,12 +21771,12 @@
       </c>
       <c r="D124" s="7" t="inlineStr">
         <is>
-          <t>Al Nasraniya</t>
+          <t>Al Fanar</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476659, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-FANAR/9986582/636025824</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr"/>
@@ -21748,7 +21784,7 @@
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Hull 2585 (Hanwha)</t>
+          <t>Hull H1795A</t>
         </is>
       </c>
       <c r="J124" s="4" t="inlineStr">
@@ -21778,7 +21814,7 @@
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>MOL, COSCO</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
@@ -21790,7 +21826,7 @@
       <c r="R124" s="2" t="inlineStr"/>
       <c r="S124" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>Hudong-Zhonghua Shipbuilding</t>
         </is>
       </c>
       <c r="T124" s="4" t="inlineStr">
@@ -21800,27 +21836,27 @@
       </c>
       <c r="U124" s="4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>https://www.shipyards.gr/shipyards/new-buildings-shipyards/newbuilding-farest-pacific-ocean/newbuilding-far-east-china-sea/china-south/hudong-zhonghua-shipbuilding-group-coltd</t>
         </is>
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>31.271988</t>
         </is>
       </c>
       <c r="X124" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>121.575478</t>
         </is>
       </c>
       <c r="Y124" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>7HCG+R4 Pudong, Shanghai, China</t>
         </is>
       </c>
       <c r="Z124" s="4" t="inlineStr">
@@ -21830,7 +21866,7 @@
       </c>
       <c r="AA124" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hudong-Zhonghua+Shipbuilding/@31.2720706,121.5727207,753m/data=!3m2!1e3!4b1!4m6!3m5!1s0x35b2742eceeb203d:0x37fddc7176d2cc24!8m2!3d31.2720706!4d121.5752956!16s%2Fg%2F1td0qx6d?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB124" s="4" t="inlineStr">
@@ -21864,7 +21900,7 @@
       </c>
       <c r="AK124" s="4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="AL124" s="4" t="inlineStr">
@@ -21888,12 +21924,12 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>1069845</t>
+          <t>9994034</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -21901,32 +21937,24 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>Al Yousifiya</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/476660, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Clean Rio Grande</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr"/>
       <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2586 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
-      <c r="K125" s="4" t="inlineStr">
-        <is>
-          <t>on order</t>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
       <c r="L125" s="4" t="inlineStr">
@@ -21939,14 +21967,14 @@
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="N125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/466740, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
         </is>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>Dynagas</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -21958,7 +21986,7 @@
       <c r="R125" s="2" t="inlineStr"/>
       <c r="S125" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>HD Hyundai Heavy Industries</t>
         </is>
       </c>
       <c r="T125" s="4" t="inlineStr">
@@ -21973,22 +22001,22 @@
       </c>
       <c r="V125" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>https://www.hd.com/en/main</t>
         </is>
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>35.51613</t>
         </is>
       </c>
       <c r="X125" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>129.4383</t>
         </is>
       </c>
       <c r="Y125" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>GC8Q+M6 Ulsan</t>
         </is>
       </c>
       <c r="Z125" s="4" t="inlineStr">
@@ -21998,12 +22026,12 @@
       </c>
       <c r="AA125" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB125" s="4" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="AC125" s="4" t="inlineStr">
@@ -22022,7 +22050,7 @@
       <c r="AH125" s="2" t="inlineStr"/>
       <c r="AI125" s="4" t="inlineStr">
         <is>
-          <t>X-DF</t>
+          <t>ME-GA</t>
         </is>
       </c>
       <c r="AJ125" s="4" t="inlineStr">
@@ -22030,14 +22058,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK125" s="4" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="AL125" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="AK125" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AL125" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/466740, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
         </is>
       </c>
       <c r="AM125" s="4" t="inlineStr">
@@ -22056,12 +22084,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>1069869</t>
+          <t>9994008</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -22069,32 +22097,24 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D126" s="7" t="inlineStr">
-        <is>
-          <t>Athba</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>https://www.shipvault.com/ships/476661, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Clean Texas</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr"/>
       <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2587 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
-      <c r="K126" s="4" t="inlineStr">
-        <is>
-          <t>on order</t>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
       <c r="L126" s="4" t="inlineStr">
@@ -22107,14 +22127,14 @@
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="N126" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="N126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/466739, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
         </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>Dynagas</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -22126,7 +22146,7 @@
       <c r="R126" s="2" t="inlineStr"/>
       <c r="S126" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>HD Hyundai Heavy Industries</t>
         </is>
       </c>
       <c r="T126" s="4" t="inlineStr">
@@ -22141,22 +22161,22 @@
       </c>
       <c r="V126" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>https://www.hd.com/en/main</t>
         </is>
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>35.51613</t>
         </is>
       </c>
       <c r="X126" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>129.4383</t>
         </is>
       </c>
       <c r="Y126" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>GC8Q+M6 Ulsan</t>
         </is>
       </c>
       <c r="Z126" s="4" t="inlineStr">
@@ -22166,12 +22186,12 @@
       </c>
       <c r="AA126" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB126" s="4" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="AC126" s="4" t="inlineStr">
@@ -22190,7 +22210,7 @@
       <c r="AH126" s="2" t="inlineStr"/>
       <c r="AI126" s="4" t="inlineStr">
         <is>
-          <t>X-DF</t>
+          <t>ME-GA</t>
         </is>
       </c>
       <c r="AJ126" s="4" t="inlineStr">
@@ -22198,14 +22218,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK126" s="4" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="AL126" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="AK126" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AL126" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/466739, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
         </is>
       </c>
       <c r="AM126" s="4" t="inlineStr">
@@ -22224,12 +22244,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>1069871</t>
+          <t>1058327</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -22239,27 +22259,19 @@
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>E Qab</t>
+          <t>Prime Creativity</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476662, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-CREATIVITY/1058327/1</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr"/>
       <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2588 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -22282,7 +22294,7 @@
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>China Energy Shipping</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
@@ -22294,7 +22306,7 @@
       <c r="R127" s="2" t="inlineStr"/>
       <c r="S127" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
         </is>
       </c>
       <c r="T127" s="4" t="inlineStr">
@@ -22304,27 +22316,27 @@
       </c>
       <c r="U127" s="4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="V127" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
         </is>
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>38.937861</t>
         </is>
       </c>
       <c r="X127" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>121.638613</t>
         </is>
       </c>
       <c r="Y127" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
         </is>
       </c>
       <c r="Z127" s="4" t="inlineStr">
@@ -22334,12 +22346,12 @@
       </c>
       <c r="AA127" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB127" s="4" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="AC127" s="4" t="inlineStr">
@@ -22368,7 +22380,7 @@
       </c>
       <c r="AK127" s="4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="AL127" s="4" t="inlineStr">
@@ -22392,12 +22404,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>1069895</t>
+          <t>1030569</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -22405,29 +22417,21 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D128" s="7" t="inlineStr">
-        <is>
-          <t>Ghash Sham</t>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Alliance Venture</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478215, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
+          <t>https://www.shipvault.com/ships/469428, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469428, https://www.marinetraffic.org/ship-owner-manager-ism-data/ALLIANCE-VENTURE/1030569/1</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr"/>
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2589 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -22450,7 +22454,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>Wah Kwong, China Gas, CSSC</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -22462,7 +22466,7 @@
       <c r="R128" s="2" t="inlineStr"/>
       <c r="S128" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
         </is>
       </c>
       <c r="T128" s="4" t="inlineStr">
@@ -22472,27 +22476,27 @@
       </c>
       <c r="U128" s="4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="V128" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
         </is>
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>38.937861</t>
         </is>
       </c>
       <c r="X128" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>121.638613</t>
         </is>
       </c>
       <c r="Y128" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
         </is>
       </c>
       <c r="Z128" s="4" t="inlineStr">
@@ -22502,12 +22506,12 @@
       </c>
       <c r="AA128" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB128" s="4" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="AC128" s="4" t="inlineStr">
@@ -22536,7 +22540,7 @@
       </c>
       <c r="AK128" s="4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="AL128" s="4" t="inlineStr">
@@ -22560,12 +22564,12 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>1069924</t>
+          <t>1058315</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -22575,27 +22579,19 @@
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Al Egdah</t>
+          <t>Prime Unity</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478216, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-UNITY/1058315/1</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr"/>
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2590 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -22618,7 +22614,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>China Energy Shipping</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -22630,7 +22626,7 @@
       <c r="R129" s="2" t="inlineStr"/>
       <c r="S129" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
         </is>
       </c>
       <c r="T129" s="4" t="inlineStr">
@@ -22640,27 +22636,27 @@
       </c>
       <c r="U129" s="4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="V129" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
         </is>
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>38.937861</t>
         </is>
       </c>
       <c r="X129" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>121.638613</t>
         </is>
       </c>
       <c r="Y129" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
         </is>
       </c>
       <c r="Z129" s="4" t="inlineStr">
@@ -22670,12 +22666,12 @@
       </c>
       <c r="AA129" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB129" s="4" t="inlineStr">
         <is>
-          <t>174000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="AC129" s="4" t="inlineStr">
@@ -22704,7 +22700,7 @@
       </c>
       <c r="AK129" s="4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="AL129" s="4" t="inlineStr">
@@ -22728,12 +22724,12 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>1069936</t>
+          <t>9980552</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -22741,32 +22737,24 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
-        <is>
-          <t>Al Khbaib</t>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Elisa Halcyon</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478217, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185, https://www.marinetraffic.org/ship-owner-manager-ism-data/ELISA-HALCYON/9980552/228488900</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr"/>
       <c r="G130" s="2" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2591 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
-      <c r="K130" s="4" t="inlineStr">
-        <is>
-          <t>on order</t>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>active</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
@@ -22779,14 +22767,14 @@
           <t>12/31/2024</t>
         </is>
       </c>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="N130" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
         </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>NYK Line</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
@@ -22798,7 +22786,7 @@
       <c r="R130" s="2" t="inlineStr"/>
       <c r="S130" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>HD Hyundai Samho</t>
         </is>
       </c>
       <c r="T130" s="4" t="inlineStr">
@@ -22813,22 +22801,22 @@
       </c>
       <c r="V130" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>https://www.hshi.co.kr/eng/</t>
         </is>
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>34.75031</t>
         </is>
       </c>
       <c r="X130" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>126.3875</t>
         </is>
       </c>
       <c r="Y130" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>Q92P+7M Yeongam-gun, Jeollanam-do</t>
         </is>
       </c>
       <c r="Z130" s="4" t="inlineStr">
@@ -22838,7 +22826,7 @@
       </c>
       <c r="AA130" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hyundai+Samho+Heavy+Industries+Entrance/data=!3m1!1e3!4m10!1m2!2m1!1sHyundai+Samho+Heavy+Industries!3m6!1s0x3573a4568dfe21d7:0x865a025eb9b373b5!8m2!3d34.75066!4d126.386691!15sCh5IeXVuZGFpIFNhbWhvIEhlYXZ5IEluZHVzdHJpZXOSAQhidXNfc3RvcOABAA!16s%2Fg%2F11b77sqk26?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB130" s="4" t="inlineStr">
@@ -22870,14 +22858,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="AK130" s="4" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="AL130" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+      <c r="AK130" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AL130" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/461185, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
         </is>
       </c>
       <c r="AM130" s="4" t="inlineStr">
@@ -22896,12 +22884,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>639</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>1069948</t>
+          <t>1056410</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -22911,27 +22899,19 @@
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Khowzan</t>
+          <t>Solidarity</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478218, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/SOLIDARITY/1056410/1</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr"/>
       <c r="G131" s="2" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" s="4" t="inlineStr">
-        <is>
-          <t>Hull 2592 (Hanwha)</t>
-        </is>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
-        </is>
-      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -22954,7 +22934,7 @@
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>MOL</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
@@ -22966,7 +22946,7 @@
       <c r="R131" s="2" t="inlineStr"/>
       <c r="S131" s="4" t="inlineStr">
         <is>
-          <t>Hanwha Ocean</t>
+          <t>HD Hyundai Heavy Industries</t>
         </is>
       </c>
       <c r="T131" s="4" t="inlineStr">
@@ -22981,22 +22961,22 @@
       </c>
       <c r="V131" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+          <t>https://www.hd.com/en/main</t>
         </is>
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>34.87385</t>
+          <t>35.51613</t>
         </is>
       </c>
       <c r="X131" s="4" t="inlineStr">
         <is>
-          <t>128.6966</t>
+          <t>129.4383</t>
         </is>
       </c>
       <c r="Y131" s="4" t="inlineStr">
         <is>
-          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+          <t>GC8Q+M6 Ulsan</t>
         </is>
       </c>
       <c r="Z131" s="4" t="inlineStr">
@@ -23006,7 +22986,7 @@
       </c>
       <c r="AA131" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB131" s="4" t="inlineStr">
@@ -23030,7 +23010,7 @@
       <c r="AH131" s="2" t="inlineStr"/>
       <c r="AI131" s="4" t="inlineStr">
         <is>
-          <t>X-DF</t>
+          <t>DFDE</t>
         </is>
       </c>
       <c r="AJ131" s="4" t="inlineStr">
@@ -23040,7 +23020,7 @@
       </c>
       <c r="AK131" s="4" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="AL131" s="4" t="inlineStr">
@@ -23064,12 +23044,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>1069950</t>
+          <t>1069821</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -23079,12 +23059,12 @@
       </c>
       <c r="D132" s="7" t="inlineStr">
         <is>
-          <t>Al Ghafat</t>
+          <t>Al Nasraniya</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478219, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
+          <t>https://www.shipvault.com/ships/476659, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -23092,7 +23072,7 @@
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" s="4" t="inlineStr">
         <is>
-          <t>Hull 2693 (Hanwha)</t>
+          <t>Hull 2585 (Hanwha)</t>
         </is>
       </c>
       <c r="J132" s="4" t="inlineStr">
@@ -23122,7 +23102,7 @@
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>K Line / Hyundai Glovis</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
@@ -23232,12 +23212,12 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>1069962</t>
+          <t>1069845</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -23247,12 +23227,12 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Al Sidriya</t>
+          <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478220, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
+          <t>https://www.shipvault.com/ships/476660, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -23260,7 +23240,7 @@
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>Hull 2694 (Hanwha)</t>
+          <t>Hull 2586 (Hanwha)</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
@@ -23290,7 +23270,7 @@
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>K Line / Hyundai Glovis</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
@@ -23400,12 +23380,12 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>1070727</t>
+          <t>1069869</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -23415,12 +23395,12 @@
       </c>
       <c r="D134" s="7" t="inlineStr">
         <is>
-          <t>Lekhraib</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479139, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+          <t>https://www.shipvault.com/ships/476661, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -23428,7 +23408,7 @@
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" s="4" t="inlineStr">
         <is>
-          <t>Hull 2694 (SHI)</t>
+          <t>Hull 2587 (Hanwha)</t>
         </is>
       </c>
       <c r="J134" s="4" t="inlineStr">
@@ -23458,7 +23438,7 @@
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>CMES</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
@@ -23470,7 +23450,7 @@
       <c r="R134" s="2" t="inlineStr"/>
       <c r="S134" s="4" t="inlineStr">
         <is>
-          <t>Samsung Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T134" s="4" t="inlineStr">
@@ -23485,22 +23465,22 @@
       </c>
       <c r="V134" s="4" t="inlineStr">
         <is>
-          <t>https://www.samsungshi.com/En/Default.aspx</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>34.89804</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X134" s="4" t="inlineStr">
         <is>
-          <t>128.6045</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y134" s="4" t="inlineStr">
         <is>
-          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z134" s="4" t="inlineStr">
@@ -23510,7 +23490,7 @@
       </c>
       <c r="AA134" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB134" s="4" t="inlineStr">
@@ -23568,12 +23548,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>1069974</t>
+          <t>1069871</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -23583,12 +23563,12 @@
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Ain Snan</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478221, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+          <t>https://www.shipvault.com/ships/476662, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -23596,7 +23576,7 @@
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>Hull 2695 (Hanwha)</t>
+          <t>Hull 2588 (Hanwha)</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
@@ -23626,7 +23606,7 @@
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>K Line / Hyundai Glovis</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
@@ -23736,12 +23716,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>1069986</t>
+          <t>1069895</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -23751,12 +23731,12 @@
       </c>
       <c r="D136" s="7" t="inlineStr">
         <is>
-          <t>Al Wasmi</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478222, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+          <t>https://www.shipvault.com/ships/478215, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -23764,7 +23744,7 @@
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="4" t="inlineStr">
         <is>
-          <t>Hull 2696 (Hanwha)</t>
+          <t>Hull 2589 (Hanwha)</t>
         </is>
       </c>
       <c r="J136" s="4" t="inlineStr">
@@ -23794,7 +23774,7 @@
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>K Line / Hyundai Glovis</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
@@ -23904,12 +23884,12 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>1070739</t>
+          <t>1069924</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -23919,12 +23899,12 @@
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Wadi Al Askar</t>
+          <t>Al Egdah</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479141, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+          <t>https://www.shipvault.com/ships/478216, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -23932,7 +23912,7 @@
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>Hull 2696 (SHI)</t>
+          <t>Hull 2590 (Hanwha)</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
@@ -23962,7 +23942,7 @@
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>CMES</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
@@ -23974,7 +23954,7 @@
       <c r="R137" s="2" t="inlineStr"/>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>Samsung Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T137" s="4" t="inlineStr">
@@ -23989,22 +23969,22 @@
       </c>
       <c r="V137" s="4" t="inlineStr">
         <is>
-          <t>https://www.samsungshi.com/En/Default.aspx</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>34.89804</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X137" s="4" t="inlineStr">
         <is>
-          <t>128.6045</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y137" s="4" t="inlineStr">
         <is>
-          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z137" s="4" t="inlineStr">
@@ -24014,7 +23994,7 @@
       </c>
       <c r="AA137" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB137" s="4" t="inlineStr">
@@ -24072,12 +24052,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>1070741</t>
+          <t>1069936</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -24087,12 +24067,12 @@
       </c>
       <c r="D138" s="7" t="inlineStr">
         <is>
-          <t>Al Shaheen</t>
+          <t>Al Khbaib</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479144, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+          <t>https://www.shipvault.com/ships/478217, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -24100,7 +24080,7 @@
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>Hull 2699 (SHI)</t>
+          <t>Hull 2591 (Hanwha)</t>
         </is>
       </c>
       <c r="J138" s="4" t="inlineStr">
@@ -24130,7 +24110,7 @@
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>CMES</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
@@ -24142,7 +24122,7 @@
       <c r="R138" s="2" t="inlineStr"/>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>Samsung Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T138" s="4" t="inlineStr">
@@ -24157,22 +24137,22 @@
       </c>
       <c r="V138" s="4" t="inlineStr">
         <is>
-          <t>https://www.samsungshi.com/En/Default.aspx</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>34.89804</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X138" s="4" t="inlineStr">
         <is>
-          <t>128.6045</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y138" s="4" t="inlineStr">
         <is>
-          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z138" s="4" t="inlineStr">
@@ -24182,7 +24162,7 @@
       </c>
       <c r="AA138" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB138" s="4" t="inlineStr">
@@ -24240,12 +24220,12 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>1070820</t>
+          <t>1069948</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -24255,12 +24235,12 @@
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Khowzan</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479151, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+          <t>https://www.shipvault.com/ships/478218, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -24268,7 +24248,7 @@
       <c r="H139" s="2" t="inlineStr"/>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>Hull 2706 (SHI)</t>
+          <t>Hull 2592 (Hanwha)</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
@@ -24298,7 +24278,7 @@
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>CMES</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
@@ -24310,7 +24290,7 @@
       <c r="R139" s="2" t="inlineStr"/>
       <c r="S139" s="4" t="inlineStr">
         <is>
-          <t>Samsung Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T139" s="4" t="inlineStr">
@@ -24325,22 +24305,22 @@
       </c>
       <c r="V139" s="4" t="inlineStr">
         <is>
-          <t>https://www.samsungshi.com/En/Default.aspx</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>34.89804</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X139" s="4" t="inlineStr">
         <is>
-          <t>128.6045</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y139" s="4" t="inlineStr">
         <is>
-          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z139" s="4" t="inlineStr">
@@ -24350,7 +24330,7 @@
       </c>
       <c r="AA139" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB139" s="4" t="inlineStr">
@@ -24408,12 +24388,12 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>1049091</t>
+          <t>1069950</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -24423,12 +24403,12 @@
       </c>
       <c r="D140" s="7" t="inlineStr">
         <is>
-          <t>Izghawa</t>
+          <t>Al Ghafat</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478320, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+          <t>https://www.shipvault.com/ships/478219, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -24436,7 +24416,7 @@
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>Hull 3491 (HDHHI)</t>
+          <t>Hull 2693 (Hanwha)</t>
         </is>
       </c>
       <c r="J140" s="4" t="inlineStr">
@@ -24466,7 +24446,7 @@
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>K Line / Hyundai Glovis</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
@@ -24478,7 +24458,7 @@
       <c r="R140" s="2" t="inlineStr"/>
       <c r="S140" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T140" s="4" t="inlineStr">
@@ -24493,22 +24473,22 @@
       </c>
       <c r="V140" s="4" t="inlineStr">
         <is>
-          <t>https://www.hd.com/en/main</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>35.51613</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X140" s="4" t="inlineStr">
         <is>
-          <t>129.4383</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y140" s="4" t="inlineStr">
         <is>
-          <t>GC8Q+M6 Ulsan</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z140" s="4" t="inlineStr">
@@ -24518,7 +24498,7 @@
       </c>
       <c r="AA140" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB140" s="4" t="inlineStr">
@@ -24576,12 +24556,12 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>1049118</t>
+          <t>1069962</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -24591,12 +24571,12 @@
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Al Wa'ab</t>
+          <t>Al Sidriya</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478321, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+          <t>https://www.shipvault.com/ships/478220, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -24604,7 +24584,7 @@
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>Hull 3492 (HDHHI)</t>
+          <t>Hull 2694 (Hanwha)</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
@@ -24634,7 +24614,7 @@
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>K Line / Hyundai Glovis</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
@@ -24646,7 +24626,7 @@
       <c r="R141" s="2" t="inlineStr"/>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Heavy Industries</t>
+          <t>Hanwha Ocean</t>
         </is>
       </c>
       <c r="T141" s="4" t="inlineStr">
@@ -24661,22 +24641,22 @@
       </c>
       <c r="V141" s="4" t="inlineStr">
         <is>
-          <t>https://www.hd.com/en/main</t>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
         </is>
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>35.51613</t>
+          <t>34.87385</t>
         </is>
       </c>
       <c r="X141" s="4" t="inlineStr">
         <is>
-          <t>129.4383</t>
+          <t>128.6966</t>
         </is>
       </c>
       <c r="Y141" s="4" t="inlineStr">
         <is>
-          <t>GC8Q+M6 Ulsan</t>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z141" s="4" t="inlineStr">
@@ -24686,7 +24666,7 @@
       </c>
       <c r="AA141" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB141" s="4" t="inlineStr">
@@ -24744,12 +24724,12 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>1030557</t>
+          <t>1070727</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -24759,19 +24739,27 @@
       </c>
       <c r="D142" s="7" t="inlineStr">
         <is>
-          <t>Friendship Venture</t>
+          <t>Lekhraib</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469427, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427</t>
+          <t>https://www.shipvault.com/ships/479139, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr"/>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2694 (SHI)</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
       <c r="K142" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -24794,7 +24782,7 @@
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>Wah Kwong, China Gas, CSSC</t>
+          <t>CMES</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
@@ -24806,7 +24794,7 @@
       <c r="R142" s="2" t="inlineStr"/>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+          <t>Samsung Heavy Industries</t>
         </is>
       </c>
       <c r="T142" s="4" t="inlineStr">
@@ -24816,27 +24804,27 @@
       </c>
       <c r="U142" s="4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="V142" s="4" t="inlineStr">
         <is>
-          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+          <t>https://www.samsungshi.com/En/Default.aspx</t>
         </is>
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>38.937861</t>
+          <t>34.89804</t>
         </is>
       </c>
       <c r="X142" s="4" t="inlineStr">
         <is>
-          <t>121.638613</t>
+          <t>128.6045</t>
         </is>
       </c>
       <c r="Y142" s="4" t="inlineStr">
         <is>
-          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z142" s="4" t="inlineStr">
@@ -24846,12 +24834,12 @@
       </c>
       <c r="AA142" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB142" s="4" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="AC142" s="4" t="inlineStr">
@@ -24900,6 +24888,1502 @@
       <c r="AR142" s="2" t="inlineStr"/>
       <c r="AS142" s="2" t="inlineStr"/>
       <c r="AT142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>1069974</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>Ain Snan</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478221, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2695 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M143" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>K Line / Hyundai Glovis</t>
+        </is>
+      </c>
+      <c r="P143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr"/>
+      <c r="R143" s="2" t="inlineStr"/>
+      <c r="S143" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean</t>
+        </is>
+      </c>
+      <c r="T143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U143" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+        </is>
+      </c>
+      <c r="W143" s="4" t="inlineStr">
+        <is>
+          <t>34.87385</t>
+        </is>
+      </c>
+      <c r="X143" s="4" t="inlineStr">
+        <is>
+          <t>128.6966</t>
+        </is>
+      </c>
+      <c r="Y143" s="4" t="inlineStr">
+        <is>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z143" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB143" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC143" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE143" s="2" t="inlineStr"/>
+      <c r="AF143" s="2" t="inlineStr"/>
+      <c r="AG143" s="2" t="inlineStr"/>
+      <c r="AH143" s="2" t="inlineStr"/>
+      <c r="AI143" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK143" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM143" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN143" s="2" t="inlineStr"/>
+      <c r="AO143" s="2" t="inlineStr"/>
+      <c r="AP143" s="2" t="inlineStr"/>
+      <c r="AQ143" s="2" t="inlineStr"/>
+      <c r="AR143" s="2" t="inlineStr"/>
+      <c r="AS143" s="2" t="inlineStr"/>
+      <c r="AT143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>1069986</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>Al Wasmi</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478222, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2696 (Hanwha)</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M144" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>K Line / Hyundai Glovis</t>
+        </is>
+      </c>
+      <c r="P144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="4" t="inlineStr">
+        <is>
+          <t>Hanwha Ocean</t>
+        </is>
+      </c>
+      <c r="T144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U144" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hanwha.com/companies/hanwha-ocean.do</t>
+        </is>
+      </c>
+      <c r="W144" s="4" t="inlineStr">
+        <is>
+          <t>34.87385</t>
+        </is>
+      </c>
+      <c r="X144" s="4" t="inlineStr">
+        <is>
+          <t>128.6966</t>
+        </is>
+      </c>
+      <c r="Y144" s="4" t="inlineStr">
+        <is>
+          <t>VMCW+V7 Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z144" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Hanwha+Ocean/data=!3m1!1e3!4m10!1m2!2m1!1sHanwha+Ocean!3m6!1s0x356ecd1d7a72f7db:0x3bfe90e7d8bf93f0!8m2!3d34.8721913!4d128.6956963!15sCgxIYW53aGEgT2NlYW5aDiIMaGFud2hhIG9jZWFukgEfc2hpcGJ1aWxkaW5nX2FuZF9yZXBhaXJfY29tcGFueZoBI0NoWkRTVWhOTUc5blMwVkpRMEZuVFVSUmRYVkVTMWhuRUFF4AEA-gEECAAQLA!16s%2Fg%2F11swmd6_76?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB144" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC144" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE144" s="2" t="inlineStr"/>
+      <c r="AF144" s="2" t="inlineStr"/>
+      <c r="AG144" s="2" t="inlineStr"/>
+      <c r="AH144" s="2" t="inlineStr"/>
+      <c r="AI144" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK144" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM144" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN144" s="2" t="inlineStr"/>
+      <c r="AO144" s="2" t="inlineStr"/>
+      <c r="AP144" s="2" t="inlineStr"/>
+      <c r="AQ144" s="2" t="inlineStr"/>
+      <c r="AR144" s="2" t="inlineStr"/>
+      <c r="AS144" s="2" t="inlineStr"/>
+      <c r="AT144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>1070739</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D145" s="7" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479141, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2696 (SHI)</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>CMES</t>
+        </is>
+      </c>
+      <c r="P145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr"/>
+      <c r="R145" s="2" t="inlineStr"/>
+      <c r="S145" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U145" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.samsungshi.com/En/Default.aspx</t>
+        </is>
+      </c>
+      <c r="W145" s="4" t="inlineStr">
+        <is>
+          <t>34.89804</t>
+        </is>
+      </c>
+      <c r="X145" s="4" t="inlineStr">
+        <is>
+          <t>128.6045</t>
+        </is>
+      </c>
+      <c r="Y145" s="4" t="inlineStr">
+        <is>
+          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z145" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB145" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC145" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE145" s="2" t="inlineStr"/>
+      <c r="AF145" s="2" t="inlineStr"/>
+      <c r="AG145" s="2" t="inlineStr"/>
+      <c r="AH145" s="2" t="inlineStr"/>
+      <c r="AI145" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK145" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM145" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN145" s="2" t="inlineStr"/>
+      <c r="AO145" s="2" t="inlineStr"/>
+      <c r="AP145" s="2" t="inlineStr"/>
+      <c r="AQ145" s="2" t="inlineStr"/>
+      <c r="AR145" s="2" t="inlineStr"/>
+      <c r="AS145" s="2" t="inlineStr"/>
+      <c r="AT145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>1070741</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479144, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr"/>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2699 (SHI)</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M146" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>CMES</t>
+        </is>
+      </c>
+      <c r="P146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr"/>
+      <c r="R146" s="2" t="inlineStr"/>
+      <c r="S146" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U146" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.samsungshi.com/En/Default.aspx</t>
+        </is>
+      </c>
+      <c r="W146" s="4" t="inlineStr">
+        <is>
+          <t>34.89804</t>
+        </is>
+      </c>
+      <c r="X146" s="4" t="inlineStr">
+        <is>
+          <t>128.6045</t>
+        </is>
+      </c>
+      <c r="Y146" s="4" t="inlineStr">
+        <is>
+          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z146" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB146" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC146" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE146" s="2" t="inlineStr"/>
+      <c r="AF146" s="2" t="inlineStr"/>
+      <c r="AG146" s="2" t="inlineStr"/>
+      <c r="AH146" s="2" t="inlineStr"/>
+      <c r="AI146" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK146" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM146" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN146" s="2" t="inlineStr"/>
+      <c r="AO146" s="2" t="inlineStr"/>
+      <c r="AP146" s="2" t="inlineStr"/>
+      <c r="AQ146" s="2" t="inlineStr"/>
+      <c r="AR146" s="2" t="inlineStr"/>
+      <c r="AS146" s="2" t="inlineStr"/>
+      <c r="AT146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>1070820</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D147" s="7" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479151, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr"/>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>Hull 2706 (SHI)</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M147" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>CMES</t>
+        </is>
+      </c>
+      <c r="P147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr"/>
+      <c r="R147" s="2" t="inlineStr"/>
+      <c r="S147" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U147" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.samsungshi.com/En/Default.aspx</t>
+        </is>
+      </c>
+      <c r="W147" s="4" t="inlineStr">
+        <is>
+          <t>34.89804</t>
+        </is>
+      </c>
+      <c r="X147" s="4" t="inlineStr">
+        <is>
+          <t>128.6045</t>
+        </is>
+      </c>
+      <c r="Y147" s="4" t="inlineStr">
+        <is>
+          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
+        </is>
+      </c>
+      <c r="Z147" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB147" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC147" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE147" s="2" t="inlineStr"/>
+      <c r="AF147" s="2" t="inlineStr"/>
+      <c r="AG147" s="2" t="inlineStr"/>
+      <c r="AH147" s="2" t="inlineStr"/>
+      <c r="AI147" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK147" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM147" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN147" s="2" t="inlineStr"/>
+      <c r="AO147" s="2" t="inlineStr"/>
+      <c r="AP147" s="2" t="inlineStr"/>
+      <c r="AQ147" s="2" t="inlineStr"/>
+      <c r="AR147" s="2" t="inlineStr"/>
+      <c r="AS147" s="2" t="inlineStr"/>
+      <c r="AT147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>1049091</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478320, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr"/>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>Hull 3491 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M148" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>Nakilat</t>
+        </is>
+      </c>
+      <c r="P148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr"/>
+      <c r="S148" s="4" t="inlineStr">
+        <is>
+          <t>HD Hyundai Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U148" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hd.com/en/main</t>
+        </is>
+      </c>
+      <c r="W148" s="4" t="inlineStr">
+        <is>
+          <t>35.51613</t>
+        </is>
+      </c>
+      <c r="X148" s="4" t="inlineStr">
+        <is>
+          <t>129.4383</t>
+        </is>
+      </c>
+      <c r="Y148" s="4" t="inlineStr">
+        <is>
+          <t>GC8Q+M6 Ulsan</t>
+        </is>
+      </c>
+      <c r="Z148" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB148" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC148" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE148" s="2" t="inlineStr"/>
+      <c r="AF148" s="2" t="inlineStr"/>
+      <c r="AG148" s="2" t="inlineStr"/>
+      <c r="AH148" s="2" t="inlineStr"/>
+      <c r="AI148" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK148" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM148" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN148" s="2" t="inlineStr"/>
+      <c r="AO148" s="2" t="inlineStr"/>
+      <c r="AP148" s="2" t="inlineStr"/>
+      <c r="AQ148" s="2" t="inlineStr"/>
+      <c r="AR148" s="2" t="inlineStr"/>
+      <c r="AS148" s="2" t="inlineStr"/>
+      <c r="AT148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>1049118</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478321, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr"/>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>Hull 3492 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>Nakilat</t>
+        </is>
+      </c>
+      <c r="P149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr"/>
+      <c r="R149" s="2" t="inlineStr"/>
+      <c r="S149" s="4" t="inlineStr">
+        <is>
+          <t>HD Hyundai Heavy Industries</t>
+        </is>
+      </c>
+      <c r="T149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U149" s="4" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="V149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hd.com/en/main</t>
+        </is>
+      </c>
+      <c r="W149" s="4" t="inlineStr">
+        <is>
+          <t>35.51613</t>
+        </is>
+      </c>
+      <c r="X149" s="4" t="inlineStr">
+        <is>
+          <t>129.4383</t>
+        </is>
+      </c>
+      <c r="Y149" s="4" t="inlineStr">
+        <is>
+          <t>GC8Q+M6 Ulsan</t>
+        </is>
+      </c>
+      <c r="Z149" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB149" s="4" t="inlineStr">
+        <is>
+          <t>174000</t>
+        </is>
+      </c>
+      <c r="AC149" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE149" s="2" t="inlineStr"/>
+      <c r="AF149" s="2" t="inlineStr"/>
+      <c r="AG149" s="2" t="inlineStr"/>
+      <c r="AH149" s="2" t="inlineStr"/>
+      <c r="AI149" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK149" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM149" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN149" s="2" t="inlineStr"/>
+      <c r="AO149" s="2" t="inlineStr"/>
+      <c r="AP149" s="2" t="inlineStr"/>
+      <c r="AQ149" s="2" t="inlineStr"/>
+      <c r="AR149" s="2" t="inlineStr"/>
+      <c r="AS149" s="2" t="inlineStr"/>
+      <c r="AT149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>1069194</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Prime Glory</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>COSCO</t>
+        </is>
+      </c>
+      <c r="P150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr"/>
+      <c r="R150" s="2" t="inlineStr"/>
+      <c r="S150" s="4" t="inlineStr">
+        <is>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+        </is>
+      </c>
+      <c r="T150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U150" s="4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="V150" s="4" t="inlineStr">
+        <is>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+        </is>
+      </c>
+      <c r="W150" s="4" t="inlineStr">
+        <is>
+          <t>38.937861</t>
+        </is>
+      </c>
+      <c r="X150" s="4" t="inlineStr">
+        <is>
+          <t>121.638613</t>
+        </is>
+      </c>
+      <c r="Y150" s="4" t="inlineStr">
+        <is>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+        </is>
+      </c>
+      <c r="Z150" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB150" s="4" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="AC150" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE150" s="2" t="inlineStr"/>
+      <c r="AF150" s="2" t="inlineStr"/>
+      <c r="AG150" s="2" t="inlineStr"/>
+      <c r="AH150" s="2" t="inlineStr"/>
+      <c r="AI150" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK150" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM150" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN150" s="2" t="inlineStr"/>
+      <c r="AO150" s="2" t="inlineStr"/>
+      <c r="AP150" s="2" t="inlineStr"/>
+      <c r="AQ150" s="2" t="inlineStr"/>
+      <c r="AR150" s="2" t="inlineStr"/>
+      <c r="AS150" s="2" t="inlineStr"/>
+      <c r="AT150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>1030557</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/469427, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427, https://www.marinetraffic.org/ship-owner-manager-ism-data/FRIENDSHIP-VENTURE/1030557/636025371</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr"/>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M151" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O151" s="4" t="inlineStr">
+        <is>
+          <t>Wah Kwong, China Gas, CSSC</t>
+        </is>
+      </c>
+      <c r="P151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr"/>
+      <c r="R151" s="2" t="inlineStr"/>
+      <c r="S151" s="4" t="inlineStr">
+        <is>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+        </is>
+      </c>
+      <c r="T151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U151" s="4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="V151" s="4" t="inlineStr">
+        <is>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+        </is>
+      </c>
+      <c r="W151" s="4" t="inlineStr">
+        <is>
+          <t>38.937861</t>
+        </is>
+      </c>
+      <c r="X151" s="4" t="inlineStr">
+        <is>
+          <t>121.638613</t>
+        </is>
+      </c>
+      <c r="Y151" s="4" t="inlineStr">
+        <is>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+        </is>
+      </c>
+      <c r="Z151" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB151" s="4" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="AC151" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE151" s="2" t="inlineStr"/>
+      <c r="AF151" s="2" t="inlineStr"/>
+      <c r="AG151" s="2" t="inlineStr"/>
+      <c r="AH151" s="2" t="inlineStr"/>
+      <c r="AI151" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK151" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM151" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN151" s="2" t="inlineStr"/>
+      <c r="AO151" s="2" t="inlineStr"/>
+      <c r="AP151" s="2" t="inlineStr"/>
+      <c r="AQ151" s="2" t="inlineStr"/>
+      <c r="AR151" s="2" t="inlineStr"/>
+      <c r="AS151" s="2" t="inlineStr"/>
+      <c r="AT151" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24912,7 +26396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F427"/>
+  <dimension ref="A1:F455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -35863,7 +37347,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3476 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3476 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048918 as AL GHUWAIR (MMSI 538000000)</t>
         </is>
       </c>
     </row>
@@ -35895,14 +37379,14 @@
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3476 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3476 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048918 as AL GHUWAIR (MMSI 538000000)</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -35912,22 +37396,22 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Wadi Sultana</t>
+          <t>Al Ghuwair</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478306</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-GHUWAIR/1048918/538000000</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3477 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3476 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048918 as AL GHUWAIR (MMSI 538000000)</t>
         </is>
       </c>
     </row>
@@ -35949,24 +37433,24 @@
       </c>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306</t>
+          <t>https://www.shipvault.com/ships/478306</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3477 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3477 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048920 as WADI SULTANA</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -35976,29 +37460,29 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Lesha</t>
+          <t>Wadi Sultana</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478307</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478306</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3478 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3477 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048920 as WADI SULTANA</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -36008,29 +37492,29 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Lesha</t>
+          <t>Wadi Sultana</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/WADI-SULTANA/1048920/1</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3478 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3477 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048920 as WADI SULTANA</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -36040,12 +37524,12 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Al Jazi</t>
+          <t>Lesha</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478308</t>
+          <t>https://www.shipvault.com/ships/478307</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -36055,14 +37539,14 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3479 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3478 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048932 as LESHA</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -36072,12 +37556,12 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Al Jazi</t>
+          <t>Lesha</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478307</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
@@ -36087,14 +37571,14 @@
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3479 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3478 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048932 as LESHA</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -36104,29 +37588,29 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Al Mashrab</t>
+          <t>Lesha</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478309</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LESHA/1048932/1</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3480 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3478 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048932 as LESHA</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -36136,29 +37620,29 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Al Mashrab</t>
+          <t>Al Jazi</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309</t>
+          <t>https://www.shipvault.com/ships/478308</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3480 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3479 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048944 as AL JAZI</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -36168,29 +37652,29 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Al Mirzam</t>
+          <t>Al Jazi</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478310</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478308</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3481 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3479 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048944 as AL JAZI</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -36200,29 +37684,29 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Al Mirzam</t>
+          <t>Al Jazi</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-JAZI/1048944/1</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3481 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3479 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048944 as AL JAZI</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -36232,12 +37716,12 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Maqdeem</t>
+          <t>Al Mashrab</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478311</t>
+          <t>https://www.shipvault.com/ships/478309</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -36247,14 +37731,14 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3482 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3480 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048956 as AL MASHRAB</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
@@ -36264,12 +37748,12 @@
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Maqdeem</t>
+          <t>Al Mashrab</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478309</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -36279,14 +37763,14 @@
       </c>
       <c r="F355" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3482 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3480 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048956 as AL MASHRAB</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
@@ -36296,29 +37780,29 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Al Rufaa</t>
+          <t>Al Mashrab</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478312</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-MASHRAB/1048956/1</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3483 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3480 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048956 as AL MASHRAB</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
@@ -36328,29 +37812,29 @@
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Al Rufaa</t>
+          <t>Al Mirzam</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312</t>
+          <t>https://www.shipvault.com/ships/478310</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F357" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3483 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3481 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048982 as AL MIRZAM</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
@@ -36360,29 +37844,29 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Al Nekhsh</t>
+          <t>Al Mirzam</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478313</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478310</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3484 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3481 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048982 as AL MIRZAM</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
@@ -36392,29 +37876,29 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Al Nekhsh</t>
+          <t>Al Mirzam</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-MIRZAM/1048982/1</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F359" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3484 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3481 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048982 as AL MIRZAM</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -36424,12 +37908,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Leh'saien</t>
+          <t>Maqdeem</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478314</t>
+          <t>https://www.shipvault.com/ships/478311</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -36439,14 +37923,14 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3485 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3482 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048994 as MAQDEEM</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
@@ -36456,12 +37940,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>Leh'saien</t>
+          <t>Maqdeem</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478311</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -36471,14 +37955,14 @@
       </c>
       <c r="F361" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3485 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3482 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048994 as MAQDEEM</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
@@ -36488,29 +37972,29 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Le'shara</t>
+          <t>Maqdeem</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478315</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/MAQDEEM/1048994/1</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3486 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3482 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1048994 as MAQDEEM</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
@@ -36520,29 +38004,29 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Le'shara</t>
+          <t>Al Rufaa</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315</t>
+          <t>https://www.shipvault.com/ships/478312</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F363" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3486 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3483 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049003 as AL RUFAA</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
@@ -36552,29 +38036,29 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Librega</t>
+          <t>Al Rufaa</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478316</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478312</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3487 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3483 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049003 as AL RUFAA</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
@@ -36584,29 +38068,29 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Librega</t>
+          <t>Al Rufaa</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-RUFAA/1049003/1</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F365" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3487 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3483 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049003 as AL RUFAA</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
@@ -36616,12 +38100,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Eshairej</t>
+          <t>Al Nekhsh</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478317</t>
+          <t>https://www.shipvault.com/ships/478313</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -36631,14 +38115,14 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3488 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3484 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049015 as AL NEKHSH</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
@@ -36648,12 +38132,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Eshairej</t>
+          <t>Al Nekhsh</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478313</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -36663,14 +38147,14 @@
       </c>
       <c r="F367" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3488 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3484 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049015 as AL NEKHSH</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
@@ -36680,29 +38164,29 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Mneefa</t>
+          <t>Al Nekhsh</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478318</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NEKHSH/1049015/1</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3489 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3484 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049015 as AL NEKHSH</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
@@ -36712,29 +38196,29 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>Mneefa</t>
+          <t>Leh'saien</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318</t>
+          <t>https://www.shipvault.com/ships/478314</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F369" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3489 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3485 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049027 as LEH'SAIEN</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
@@ -36744,29 +38228,29 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Ezhara</t>
+          <t>Leh'saien</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478319</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478314</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3490 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3485 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049027 as LEH'SAIEN</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -36776,29 +38260,29 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Ezhara</t>
+          <t>Leh'saien</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LEH'SAIEN/1049027/1</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F371" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3490 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3485 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049027 as LEH'SAIEN</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -36808,12 +38292,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Al Sabsab</t>
+          <t>Le'shara</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/462933</t>
+          <t>https://www.shipvault.com/ships/478315</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -36823,14 +38307,14 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull H1794A' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3486 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049039 as LE'SHARA</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -36840,12 +38324,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Al Sabsab</t>
+          <t>Le'shara</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478315</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -36855,157 +38339,157 @@
       </c>
       <c r="F373" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull H1794A' -&gt; vessel named</t>
+          <t>placeholder 'Hull 3486 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049039 as LE'SHARA</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Le'shara</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/466740</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LE'SHARA/1049039/1</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2026-07-06, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3434; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3486 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049039 as LE'SHARA</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Librega</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
+          <t>https://www.shipvault.com/ships/478316</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F375" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2026-07-06, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3434; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3487 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049041 as LIBREGA</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Librega</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/466740</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478316</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2026-07-06 per shipvault</t>
+          <t>placeholder 'Hull 3487 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049041 as LIBREGA</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Librega</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LIBREGA/1049041/1</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F377" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2026-07-06 per shipvault</t>
+          <t>placeholder 'Hull 3487 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049041 as LIBREGA</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Eshairej</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/466739</t>
+          <t>https://www.shipvault.com/ships/478317</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -37015,29 +38499,29 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2026-04-30, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3433; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3488 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049053 as ESHAIREJ</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Eshairej</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478317</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -37047,78 +38531,78 @@
       </c>
       <c r="F379" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2026-04-30, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3433; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3488 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049053 as ESHAIREJ</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Eshairej</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/466739</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/ESHAIREJ/1049053/1</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2026-04-30 per shipvault</t>
+          <t>placeholder 'Hull 3488 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049053 as ESHAIREJ</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Mneefa</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
+          <t>https://www.shipvault.com/ships/478318</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F381" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2026-04-30 per shipvault</t>
+          <t>placeholder 'Hull 3489 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049065 as MNEEFA</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
@@ -37128,29 +38612,29 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Alliance Venture</t>
+          <t>Mneefa</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469428</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478318</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>backend 'Dalian No 1 G175K-13' differs from registry name</t>
+          <t>placeholder 'Hull 3489 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049065 as MNEEFA</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
@@ -37160,44 +38644,44 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>Alliance Venture</t>
+          <t>Mneefa</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469428</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/MNEEFA/1049065/1</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F383" s="2" t="inlineStr">
         <is>
-          <t>backend 'Dalian No 1 G175K-13' differs from registry name</t>
+          <t>placeholder 'Hull 3489 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049065 as MNEEFA</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Ezhara</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461185</t>
+          <t>https://www.shipvault.com/ships/478319</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -37207,29 +38691,29 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2025-10-31, yard HYUNDAI SAMHO HEAVY INDUSTRIES no. 8174; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3490 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049089 as EZHARA</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>Ezhara</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478319</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -37239,78 +38723,78 @@
       </c>
       <c r="F385" s="2" t="inlineStr">
         <is>
-          <t>shipvault: status ACTIVE, delivered 2025-10-31, yard HYUNDAI SAMHO HEAVY INDUSTRIES no. 8174; single-source (no vesselfinder name/MMSI)</t>
+          <t>placeholder 'Hull 3490 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049089 as EZHARA</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Ezhara</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461185</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/EZHARA/1049089/1</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2025-10-31 per shipvault</t>
+          <t>placeholder 'Hull 3490 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049089 as EZHARA</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>239</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>Delivery year</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>Diamond Gas Nexus</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/DIAMOND-GAS-NEXUS/1023877/563334400</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F387" s="2" t="inlineStr">
         <is>
-          <t>backend 2027 -&gt; delivered 2025-10-31 per shipvault</t>
+          <t>placeholder 'Hull 8208 (HSHI)' -&gt; vessel named; marinetraffic.org lists IMO 1023877 as DIAMOND GAS NEXUS (MMSI 563334400); shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>240</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
@@ -37320,29 +38804,29 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Elisa Halcyon</t>
+          <t>Grace Himawari</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/461185</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/GRACE-HIMAWARI/1023889/1</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>backend 'Elisa Halycon' differs from registry name</t>
+          <t>placeholder 'Hull 8209 (HSHI)' -&gt; vessel named; marinetraffic.org lists IMO 1023889 as GRACE HIMAWARI; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>242</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
@@ -37352,29 +38836,29 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>Elisa Halcyon</t>
+          <t>Grace Gerbera</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/GRACE-GERBERA/1023906/1</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api, shipvault_api, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F389" s="2" t="inlineStr">
         <is>
-          <t>backend 'Elisa Halycon' differs from registry name</t>
+          <t>placeholder 'Hull 8238 (HSHI)' -&gt; vessel named; marinetraffic.org lists IMO 1023906 as GRACE GERBERA; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>243</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
@@ -37384,29 +38868,29 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Al Nasraniya</t>
+          <t>Ferdy Vanguard</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476659</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/FERDY-VANGUARD/1023918/1</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 8239 (HSHI)' -&gt; vessel named; marinetraffic.org lists IMO 1023918 as FERDY VANGUARD; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
@@ -37416,29 +38900,29 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>Al Nasraniya</t>
+          <t>Al Sabsab</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
+          <t>https://www.shipvault.com/ships/462933</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F391" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull H1794A' -&gt; vessel named; marinetraffic.org independently lists IMO 9986570 as AL SABSAB (MMSI 636025823)</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
@@ -37448,29 +38932,29 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Al Yousifiya</t>
+          <t>Al Sabsab</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476660</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/462933</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull H1794A' -&gt; vessel named; marinetraffic.org independently lists IMO 9986570 as AL SABSAB (MMSI 636025823)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>258</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -37480,29 +38964,29 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>Al Yousifiya</t>
+          <t>Al Sabsab</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SABSAB/9986570/636025823</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F393" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull H1794A' -&gt; vessel named; marinetraffic.org independently lists IMO 9986570 as AL SABSAB (MMSI 636025823)</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>259</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -37512,285 +38996,285 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Athba</t>
+          <t>Al Fanar</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476661</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-FANAR/9986582/636025824</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull H1795A' -&gt; vessel named; marinetraffic.org lists IMO 9986582 as AL FANAR (MMSI 636025824); shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>Athba</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
+          <t>https://www.shipvault.com/ships/466740</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2026-07-06, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3434; marinetraffic.org shows CLEAN RIO GRANDE with MMSI 249569000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>E Qab</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476662</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2026-07-06, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3434; marinetraffic.org shows CLEAN RIO GRANDE with MMSI 249569000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>E Qab</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
+          <t>https://www.shipvault.com/ships/466740</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F397" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2026-07-06 per shipvault; marinetraffic.org shows CLEAN RIO GRANDE with MMSI 249569000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>487</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Ghash Sham</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478215</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466740</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2026-07-06 per shipvault; marinetraffic.org shows CLEAN RIO GRANDE with MMSI 249569000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>Ghash Sham</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
+          <t>https://www.shipvault.com/ships/466739</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2026-04-30, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3433; marinetraffic.org shows CLEAN TEXAS with MMSI 249342000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Al Egdah</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478216</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2026-04-30, yard HYUNDAI HEAVY INDUSTRIES CO LTD no. 3433; marinetraffic.org shows CLEAN TEXAS with MMSI 249342000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>Al Egdah</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+          <t>https://www.shipvault.com/ships/466739</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F401" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2026-04-30 per shipvault; marinetraffic.org shows CLEAN TEXAS with MMSI 249342000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>489</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Al Khbaib</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478217</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/466739</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2026-04-30 per shipvault; marinetraffic.org shows CLEAN TEXAS with MMSI 249342000 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>507</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
@@ -37800,29 +39284,29 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>Al Khbaib</t>
+          <t>Prime Creativity</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-CREATIVITY/1058327/1</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Dalian No 1 G175K-10' -&gt; vessel named; marinetraffic.org lists IMO 1058327 as PRIME CREATIVITY; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
@@ -37832,12 +39316,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Khowzan</t>
+          <t>Alliance Venture</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478218</t>
+          <t>https://www.shipvault.com/ships/469428</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -37847,14 +39331,14 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Dalian No 1 G175K-13' differs from registry name; marinetraffic.org independently lists IMO 1030569 as ALLIANCE VENTURE</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
@@ -37864,12 +39348,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>Khowzan</t>
+          <t>Alliance Venture</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469428</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -37879,14 +39363,14 @@
       </c>
       <c r="F405" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Dalian No 1 G175K-13' differs from registry name; marinetraffic.org independently lists IMO 1030569 as ALLIANCE VENTURE</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
@@ -37896,29 +39380,29 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Al Ghafat</t>
+          <t>Alliance Venture</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478219</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/ALLIANCE-VENTURE/1030569/1</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Dalian No 1 G175K-13' differs from registry name; marinetraffic.org independently lists IMO 1030569 as ALLIANCE VENTURE</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>519</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
@@ -37928,44 +39412,44 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>Al Ghafat</t>
+          <t>Prime Unity</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-UNITY/1058315/1</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Dalian No 1 G175K-9' -&gt; vessel named; marinetraffic.org lists IMO 1058315 as PRIME UNITY; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Al Sidriya</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478220</t>
+          <t>https://www.shipvault.com/ships/461185</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -37975,29 +39459,29 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2025-10-31, yard HYUNDAI SAMHO HEAVY INDUSTRIES no. 8174; marinetraffic.org shows ELISA HALCYON with MMSI 228488900 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>Al Sidriya</t>
+          <t>active</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -38007,78 +39491,78 @@
       </c>
       <c r="F409" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+          <t>shipvault: status ACTIVE, delivered 2025-10-31, yard HYUNDAI SAMHO HEAVY INDUSTRIES no. 8174; marinetraffic.org shows ELISA HALCYON with MMSI 228488900 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Lekhraib</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479139</t>
+          <t>https://www.shipvault.com/ships/461185</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2025-10-31 per shipvault; marinetraffic.org shows ELISA HALCYON with MMSI 228488900 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Delivery year</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>Lekhraib</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+          <t>backend 2027 -&gt; delivered 2025-10-31 per shipvault; marinetraffic.org shows ELISA HALCYON with MMSI 228488900 (AIS-registered) - cross-check, not cited</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
@@ -38088,29 +39572,29 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Ain Snan</t>
+          <t>Elisa Halcyon</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478221</t>
+          <t>https://www.shipvault.com/ships/461185</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api, shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Elisa Halycon' differs from registry name; marinetraffic.org independently lists IMO 9980552 as ELISA HALCYON (MMSI 228488900)</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
@@ -38120,29 +39604,29 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>Ain Snan</t>
+          <t>Elisa Halcyon</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/461185</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (shipvault_api, shipvault_api, shipvault_api))</t>
         </is>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Elisa Halycon' differs from registry name; marinetraffic.org independently lists IMO 9980552 as ELISA HALCYON (MMSI 228488900)</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>541</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
@@ -38152,29 +39636,29 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Al Wasmi</t>
+          <t>Elisa Halcyon</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478222</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/ELISA-HALCYON/9980552/228488900</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+          <t>backend 'Elisa Halycon' differs from registry name; marinetraffic.org independently lists IMO 9980552 as ELISA HALCYON (MMSI 228488900)</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>639</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
@@ -38184,29 +39668,29 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>Al Wasmi</t>
+          <t>Solidarity</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/SOLIDARITY/1056410/1</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Gdansk FSRU' -&gt; vessel named; marinetraffic.org lists IMO 1056410 as SOLIDARITY; shipvault still carries a hull placeholder - single source</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
@@ -38216,12 +39700,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Wadi Al Askar</t>
+          <t>Al Nasraniya</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479141</t>
+          <t>https://www.shipvault.com/ships/476659</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -38231,14 +39715,14 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
@@ -38248,12 +39732,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>Wadi Al Askar</t>
+          <t>Al Nasraniya</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -38263,14 +39747,14 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -38280,12 +39764,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Al Shaheen</t>
+          <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479144</t>
+          <t>https://www.shipvault.com/ships/476660</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -38295,14 +39779,14 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
@@ -38312,12 +39796,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>Al Shaheen</t>
+          <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -38327,14 +39811,14 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -38344,12 +39828,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479151</t>
+          <t>https://www.shipvault.com/ships/476661</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -38359,14 +39843,14 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -38376,12 +39860,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -38391,14 +39875,14 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -38408,12 +39892,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Izghawa</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478320</t>
+          <t>https://www.shipvault.com/ships/476662</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -38423,14 +39907,14 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -38440,12 +39924,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>Izghawa</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -38455,14 +39939,14 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -38472,12 +39956,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Al Wa'ab</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478321</t>
+          <t>https://www.shipvault.com/ships/478215</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -38487,14 +39971,14 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -38504,12 +39988,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>Al Wa'ab</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -38519,14 +40003,14 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -38536,12 +40020,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Friendship Venture</t>
+          <t>Al Egdah</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469427</t>
+          <t>https://www.shipvault.com/ships/478216</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -38551,39 +40035,935 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>backend 'Dalian No 1 G175K-12' differs from registry name</t>
+          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>Al Egdah</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>Al Khbaib</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478217</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>Al Khbaib</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>Khowzan</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478218</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>Khowzan</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>Al Ghafat</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478219</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>Al Ghafat</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>Al Sidriya</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478220</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>Al Sidriya</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>Lekhraib</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479139</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>Lekhraib</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>Ain Snan</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478221</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>Ain Snan</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>Al Wasmi</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478222</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>Al Wasmi</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479141</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479144</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479151</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478320</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478321</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>Prime Glory</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Dalian No 1 G175K-11' -&gt; vessel named; marinetraffic.org lists IMO 1069194 as PRIME GLORY; shipvault still carries a hull placeholder - single source</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="B427" s="2" t="inlineStr">
+      <c r="B453" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C427" s="2" t="inlineStr">
+      <c r="C453" s="2" t="inlineStr">
         <is>
           <t>Friendship Venture</t>
         </is>
       </c>
-      <c r="D427" s="2" t="inlineStr">
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/469427</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
         <is>
           <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427</t>
         </is>
       </c>
-      <c r="E427" s="2" t="inlineStr">
+      <c r="E454" s="2" t="inlineStr">
         <is>
           <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
-      <c r="F427" s="2" t="inlineStr">
-        <is>
-          <t>backend 'Dalian No 1 G175K-12' differs from registry name</t>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/FRIENDSHIP-VENTURE/1030557/636025371</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
         </is>
       </c>
     </row>

--- a/batches/2026-09-17_0421ET_fix_delivery_rollforward/lng_carrier_fix.xlsx
+++ b/batches/2026-09-17_0421ET_fix_delivery_rollforward/lng_carrier_fix.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Backend had not moved since June 2026. Every on-order row with an IMO was looked up in shipvault (status / delivered date / yard no.) and vesselfinder (AIS-registered name, MMSI, year built). Delivered vessels move to active with their real name; delivery years are corrected to the actual year; undelivered 2026 rows that shipvault now schedules for 2027+ are rolled forward. The rows vesselfinder never answered (IP ban at ~150/323) were cross-checked on marinetraffic.org the same afternoon (95 IMOs, paced).</t>
+          <t>Backend had not moved since June 2026. Every on-order row with an IMO was looked up in shipvault (status / delivered date / yard no.) and vesselfinder (AIS-registered name, MMSI, year built). Delivered vessels move to active with their real name; delivery years are corrected to the actual year; undelivered 2026 rows that shipvault now schedules for 2027+ are rolled forward. The rows vesselfinder never answered (IP ban at ~150/323) were cross-checked on marinetraffic.org the same afternoon (all 176 IMOs, paced, in two runs).</t>
         </is>
       </c>
     </row>
@@ -511,7 +511,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Rows corrected: 150   Refs checked: 454   Refs dropped/removed: 0</t>
+          <t>Rows corrected: 151   Refs checked: 473   Refs dropped/removed: 0</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT151"/>
+  <dimension ref="A1:AT152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23057,14 +23057,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D132" s="7" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>Al Nasraniya</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476659, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659</t>
+          <t>https://www.shipvault.com/ships/476659, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476659, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NASRANIYA/1069821/538011621</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr"/>
@@ -23225,14 +23225,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476660, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
+          <t>https://www.shipvault.com/ships/476660, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-YOUSIFIYA/1069845/1</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr"/>
@@ -23393,14 +23393,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Athba</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476661, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
+          <t>https://www.shipvault.com/ships/476661, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661, https://www.marinetraffic.org/ship-owner-manager-ism-data/ATHBA/1069869/1</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr"/>
@@ -23561,14 +23561,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D135" s="7" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>E Qab</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476662, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
+          <t>https://www.shipvault.com/ships/476662, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662, https://www.marinetraffic.org/ship-owner-manager-ism-data/E-QAB/1069871/1</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr"/>
@@ -23729,14 +23729,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D136" s="5" t="inlineStr">
         <is>
           <t>Ghash Sham</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478215, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
+          <t>https://www.shipvault.com/ships/478215, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215, https://www.marinetraffic.org/ship-owner-manager-ism-data/GHASH-SHAM/1069895/1</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr"/>
@@ -23897,14 +23897,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D137" s="7" t="inlineStr">
+      <c r="D137" s="5" t="inlineStr">
         <is>
           <t>Al Egdah</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478216, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+          <t>https://www.shipvault.com/ships/478216, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-EGDAH/1069924/1</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr"/>
@@ -24065,14 +24065,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D138" s="7" t="inlineStr">
+      <c r="D138" s="5" t="inlineStr">
         <is>
           <t>Al Khbaib</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478217, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+          <t>https://www.shipvault.com/ships/478217, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-KHBAIB/1069936/1</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr"/>
@@ -24233,14 +24233,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D139" s="7" t="inlineStr">
+      <c r="D139" s="5" t="inlineStr">
         <is>
           <t>Khowzan</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478218, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+          <t>https://www.shipvault.com/ships/478218, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218, https://www.marinetraffic.org/ship-owner-manager-ism-data/KHOWZAN/1069948/1</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr"/>
@@ -24401,14 +24401,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D140" s="7" t="inlineStr">
+      <c r="D140" s="5" t="inlineStr">
         <is>
           <t>Al Ghafat</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478219, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
+          <t>https://www.shipvault.com/ships/478219, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-GHAFAT/1069950/1</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr"/>
@@ -24569,14 +24569,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
+      <c r="D141" s="5" t="inlineStr">
         <is>
           <t>Al Sidriya</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478220, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
+          <t>https://www.shipvault.com/ships/478220, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SIDRIYA/1069962/1</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr"/>
@@ -24737,14 +24737,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D142" s="7" t="inlineStr">
+      <c r="D142" s="5" t="inlineStr">
         <is>
           <t>Lekhraib</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479139, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+          <t>https://www.shipvault.com/ships/479139, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139, https://www.marinetraffic.org/ship-owner-manager-ism-data/LEKHRAIB/1070727/477262100</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr"/>
@@ -24905,14 +24905,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="D143" s="5" t="inlineStr">
         <is>
           <t>Ain Snan</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478221, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+          <t>https://www.shipvault.com/ships/478221, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221, https://www.marinetraffic.org/ship-owner-manager-ism-data/AIN-SNAN/1069974/1</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr"/>
@@ -25073,14 +25073,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="D144" s="5" t="inlineStr">
         <is>
           <t>Al Wasmi</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478222, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+          <t>https://www.shipvault.com/ships/478222, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-WASMI/1069986/1</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr"/>
@@ -25241,14 +25241,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D145" s="7" t="inlineStr">
+      <c r="D145" s="5" t="inlineStr">
         <is>
           <t>Wadi Al Askar</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479141, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+          <t>https://www.shipvault.com/ships/479141, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141, https://www.marinetraffic.org/ship-owner-manager-ism-data/WADI-AL-ASKAR/1070739/1</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr"/>
@@ -25409,14 +25409,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D146" s="7" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>Al Shaheen</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479144, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+          <t>https://www.shipvault.com/ships/479144, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SHAHEEN/1070741/1</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr"/>
@@ -25564,12 +25564,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>150</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>1070820</t>
+          <t>1070806</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -25579,12 +25579,12 @@
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Libsayer</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479151, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LIBSAYER/1070806/1</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr"/>
@@ -25592,7 +25592,7 @@
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>Hull 2706 (SHI)</t>
+          <t>Hull 2702 (SHI)</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
@@ -25732,12 +25732,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>1049091</t>
+          <t>1070820</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -25745,14 +25745,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D148" s="7" t="inlineStr">
-        <is>
-          <t>Izghawa</t>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478320, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+          <t>https://www.shipvault.com/ships/479151, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NOUF/1070820/1</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr"/>
@@ -25760,7 +25760,7 @@
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>Hull 3491 (HDHHI)</t>
+          <t>Hull 2706 (SHI)</t>
         </is>
       </c>
       <c r="J148" s="4" t="inlineStr">
@@ -25790,7 +25790,7 @@
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>Nakilat</t>
+          <t>CMES</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
@@ -25802,7 +25802,7 @@
       <c r="R148" s="2" t="inlineStr"/>
       <c r="S148" s="4" t="inlineStr">
         <is>
-          <t>HD Hyundai Heavy Industries</t>
+          <t>Samsung Heavy Industries</t>
         </is>
       </c>
       <c r="T148" s="4" t="inlineStr">
@@ -25817,22 +25817,22 @@
       </c>
       <c r="V148" s="4" t="inlineStr">
         <is>
-          <t>https://www.hd.com/en/main</t>
+          <t>https://www.samsungshi.com/En/Default.aspx</t>
         </is>
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>35.51613</t>
+          <t>34.89804</t>
         </is>
       </c>
       <c r="X148" s="4" t="inlineStr">
         <is>
-          <t>129.4383</t>
+          <t>128.6045</t>
         </is>
       </c>
       <c r="Y148" s="4" t="inlineStr">
         <is>
-          <t>GC8Q+M6 Ulsan</t>
+          <t>VJW3+QV Geoje-si, Gyeongsangnam-do</t>
         </is>
       </c>
       <c r="Z148" s="4" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="AA148" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Samsung+Heavy+industries/data=!3m1!1e3!4m10!1m2!2m1!1ssamsung+heavy+industries!3m6!1s0x356ecd83691a8fb5:0xd4204e9a1bb0ef10!8m2!3d34.8969682!4d128.6046376!15sChhzYW1zdW5nIGhlYXZ5IGluZHVzdHJpZXOSAQhzaGlweWFyZOABAA!16s%2Fg%2F1tgcpry6?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB148" s="4" t="inlineStr">
@@ -25900,12 +25900,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>1049118</t>
+          <t>1049091</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -25913,14 +25913,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D149" s="7" t="inlineStr">
-        <is>
-          <t>Al Wa'ab</t>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478321, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+          <t>https://www.shipvault.com/ships/478320, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320, https://www.marinetraffic.org/ship-owner-manager-ism-data/IZGHAWA/1049091/1</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr"/>
@@ -25928,7 +25928,7 @@
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>Hull 3492 (HDHHI)</t>
+          <t>Hull 3491 (HDHHI)</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
@@ -26068,12 +26068,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>1069194</t>
+          <t>1049118</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -26081,21 +26081,29 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D150" s="7" t="inlineStr">
-        <is>
-          <t>Prime Glory</t>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
+          <t>https://www.shipvault.com/ships/478321, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321, https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-WA'AB/1049118/1</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr"/>
       <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr"/>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>Hull 3492 (HDHHI)</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
       <c r="K150" s="4" t="inlineStr">
         <is>
           <t>on order</t>
@@ -26118,7 +26126,7 @@
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>COSCO</t>
+          <t>Nakilat</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
@@ -26130,7 +26138,7 @@
       <c r="R150" s="2" t="inlineStr"/>
       <c r="S150" s="4" t="inlineStr">
         <is>
-          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+          <t>HD Hyundai Heavy Industries</t>
         </is>
       </c>
       <c r="T150" s="4" t="inlineStr">
@@ -26140,27 +26148,27 @@
       </c>
       <c r="U150" s="4" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="V150" s="4" t="inlineStr">
         <is>
-          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+          <t>https://www.hd.com/en/main</t>
         </is>
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>38.937861</t>
+          <t>35.51613</t>
         </is>
       </c>
       <c r="X150" s="4" t="inlineStr">
         <is>
-          <t>121.638613</t>
+          <t>129.4383</t>
         </is>
       </c>
       <c r="Y150" s="4" t="inlineStr">
         <is>
-          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+          <t>GC8Q+M6 Ulsan</t>
         </is>
       </c>
       <c r="Z150" s="4" t="inlineStr">
@@ -26170,12 +26178,12 @@
       </c>
       <c r="AA150" s="4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/HD+Hyundai+Heavy+Industries+Ulsan+Shipyard/data=!3m1!1e3!4m10!1m2!2m1!1sHD+Hyundai!3m6!1s0x3567ce56ebbfb645:0xd94a696f9fca5d90!8m2!3d35.5167468!4d129.4380269!15sCgpIRCBIeXVuZGFpkgEIc2hpcHlhcmTgAQA!16s%2Fg%2F1tfhd8y1?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
         </is>
       </c>
       <c r="AB150" s="4" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="AC150" s="4" t="inlineStr">
@@ -26228,12 +26236,12 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>508</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>1030557</t>
+          <t>1069194</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -26241,14 +26249,14 @@
           <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>Friendship Venture</t>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>Prime Glory</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469427, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427, https://www.marinetraffic.org/ship-owner-manager-ism-data/FRIENDSHIP-VENTURE/1030557/636025371</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr"/>
@@ -26278,7 +26286,7 @@
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>Wah Kwong, China Gas, CSSC</t>
+          <t>COSCO</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
@@ -26384,6 +26392,166 @@
       <c r="AR151" s="2" t="inlineStr"/>
       <c r="AS151" s="2" t="inlineStr"/>
       <c r="AT151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>1030557</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/469427, https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427, https://www.marinetraffic.org/ship-owner-manager-ism-data/FRIENDSHIP-VENTURE/1030557/636025371</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr"/>
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>on order</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>GEM</t>
+        </is>
+      </c>
+      <c r="M152" s="4" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>Wah Kwong, China Gas, CSSC</t>
+        </is>
+      </c>
+      <c r="P152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="4" t="inlineStr">
+        <is>
+          <t>DSIC (Dalian Shipbuilding Industry Co)</t>
+        </is>
+      </c>
+      <c r="T152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="U152" s="4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="V152" s="4" t="inlineStr">
+        <is>
+          <t>http://www.dsic.cn/English/CorporateProfile/AboutUs/index.htm</t>
+        </is>
+      </c>
+      <c r="W152" s="4" t="inlineStr">
+        <is>
+          <t>38.937861</t>
+        </is>
+      </c>
+      <c r="X152" s="4" t="inlineStr">
+        <is>
+          <t>121.638613</t>
+        </is>
+      </c>
+      <c r="Y152" s="4" t="inlineStr">
+        <is>
+          <t>WJMP+FX6, Binhai St, Xigang District, Dalian, Dalian, Liaoning, China, 116006</t>
+        </is>
+      </c>
+      <c r="Z152" s="4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AA152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Dalian+Shipbuilding+Heavy+Industry+Co.,Ltd./@38.9301597,121.6171177,2740m/data=!3m1!1e3!4m15!1m7!2m6!1sDalian+Shipbuilding+Industry+Co!3m4!2s60.153931,+24.928542!4m2!1d24.9285418!2d60.1539309!3m6!1s0x3585f55b64d083c7:0x46a88d8ffb6405f2!8m2!3d38.9336592!4d121.6374032!15sCh9EYWxpYW4gU2hpcGJ1aWxkaW5nIEluZHVzdHJ5IENvkgEHY29tcGFueeABAA!16s%2Fg%2F1tf_qtz_?entry=ttu&amp;g_ep=EgoyMDI1MTIwMi4wIKXMDSoASAFQAw%3D%3D</t>
+        </is>
+      </c>
+      <c r="AB152" s="4" t="inlineStr">
+        <is>
+          <t>175000</t>
+        </is>
+      </c>
+      <c r="AC152" s="4" t="inlineStr">
+        <is>
+          <t>cbm</t>
+        </is>
+      </c>
+      <c r="AD152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AE152" s="2" t="inlineStr"/>
+      <c r="AF152" s="2" t="inlineStr"/>
+      <c r="AG152" s="2" t="inlineStr"/>
+      <c r="AH152" s="2" t="inlineStr"/>
+      <c r="AI152" s="4" t="inlineStr">
+        <is>
+          <t>X-DF</t>
+        </is>
+      </c>
+      <c r="AJ152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AK152" s="4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="AL152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.igu.org/igu-reports/2025-world-lng-report</t>
+        </is>
+      </c>
+      <c r="AM152" s="4" t="inlineStr">
+        <is>
+          <t>IGU</t>
+        </is>
+      </c>
+      <c r="AN152" s="2" t="inlineStr"/>
+      <c r="AO152" s="2" t="inlineStr"/>
+      <c r="AP152" s="2" t="inlineStr"/>
+      <c r="AQ152" s="2" t="inlineStr"/>
+      <c r="AR152" s="2" t="inlineStr"/>
+      <c r="AS152" s="2" t="inlineStr"/>
+      <c r="AT152" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26396,7 +26564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F455"/>
+  <dimension ref="A1:F474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -39715,7 +39883,7 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069821 as AL NASRANIYA (MMSI 538011621)</t>
         </is>
       </c>
     </row>
@@ -39747,14 +39915,14 @@
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069821 as AL NASRANIYA (MMSI 538011621)</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
@@ -39764,22 +39932,22 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Al Yousifiya</t>
+          <t>Al Nasraniya</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476660</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NASRANIYA/1069821/538011621</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2585 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069821 as AL NASRANIYA (MMSI 538011621)</t>
         </is>
       </c>
     </row>
@@ -39801,24 +39969,24 @@
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
+          <t>https://www.shipvault.com/ships/476660</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069845 as AL YOUSIFIYA</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
@@ -39828,29 +39996,29 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Athba</t>
+          <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476661</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476660</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069845 as AL YOUSIFIYA</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
@@ -39860,29 +40028,29 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>Athba</t>
+          <t>Al Yousifiya</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-YOUSIFIYA/1069845/1</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2586 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069845 as AL YOUSIFIYA</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
@@ -39892,12 +40060,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>E Qab</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/476662</t>
+          <t>https://www.shipvault.com/ships/476661</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -39907,14 +40075,14 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069869 as ATHBA</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
@@ -39924,12 +40092,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>E Qab</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476661</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -39939,14 +40107,14 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069869 as ATHBA</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
@@ -39956,29 +40124,29 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Ghash Sham</t>
+          <t>Athba</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478215</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/ATHBA/1069869/1</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2587 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069869 as ATHBA</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
@@ -39988,29 +40156,29 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>Ghash Sham</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
+          <t>https://www.shipvault.com/ships/476662</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069871 as E QAB</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
@@ -40020,29 +40188,29 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Al Egdah</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478216</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/476662</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069871 as E QAB</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
@@ -40052,29 +40220,29 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>Al Egdah</t>
+          <t>E Qab</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/E-QAB/1069871/1</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2588 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069871 as E QAB</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -40084,12 +40252,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Al Khbaib</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478217</t>
+          <t>https://www.shipvault.com/ships/478215</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -40099,14 +40267,14 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069895 as GHASH SHAM</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
@@ -40116,12 +40284,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>Al Khbaib</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478215</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -40131,14 +40299,14 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069895 as GHASH SHAM</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
@@ -40148,29 +40316,29 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Khowzan</t>
+          <t>Ghash Sham</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478218</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/GHASH-SHAM/1069895/1</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2589 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069895 as GHASH SHAM</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
@@ -40180,29 +40348,29 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>Khowzan</t>
+          <t>Al Egdah</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
+          <t>https://www.shipvault.com/ships/478216</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069924 as AL EGDAH</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
@@ -40212,29 +40380,29 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Al Ghafat</t>
+          <t>Al Egdah</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478219</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478216</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069924 as AL EGDAH</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>85</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
@@ -40244,29 +40412,29 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>Al Ghafat</t>
+          <t>Al Egdah</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-EGDAH/1069924/1</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2590 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069924 as AL EGDAH</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
@@ -40276,12 +40444,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Al Sidriya</t>
+          <t>Al Khbaib</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478220</t>
+          <t>https://www.shipvault.com/ships/478217</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -40291,14 +40459,14 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069936 as AL KHBAIB</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
@@ -40308,12 +40476,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>Al Sidriya</t>
+          <t>Al Khbaib</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478217</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -40323,14 +40491,14 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069936 as AL KHBAIB</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>86</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
@@ -40340,29 +40508,29 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Lekhraib</t>
+          <t>Al Khbaib</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479139</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-KHBAIB/1069936/1</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2591 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069936 as AL KHBAIB</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
@@ -40372,29 +40540,29 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>Lekhraib</t>
+          <t>Khowzan</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
+          <t>https://www.shipvault.com/ships/478218</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069948 as KHOWZAN</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
@@ -40404,29 +40572,29 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Ain Snan</t>
+          <t>Khowzan</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478221</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478218</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069948 as KHOWZAN</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>88</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
@@ -40436,29 +40604,29 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>Ain Snan</t>
+          <t>Khowzan</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/KHOWZAN/1069948/1</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2592 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069948 as KHOWZAN</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
@@ -40468,12 +40636,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Al Wasmi</t>
+          <t>Al Ghafat</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478222</t>
+          <t>https://www.shipvault.com/ships/478219</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -40483,14 +40651,14 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069950 as AL GHAFAT</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
@@ -40500,12 +40668,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>Al Wasmi</t>
+          <t>Al Ghafat</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478219</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -40515,14 +40683,14 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069950 as AL GHAFAT</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
@@ -40532,29 +40700,29 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Wadi Al Askar</t>
+          <t>Al Ghafat</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479141</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-GHAFAT/1069950/1</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2693 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069950 as AL GHAFAT</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
@@ -40564,29 +40732,29 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>Wadi Al Askar</t>
+          <t>Al Sidriya</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+          <t>https://www.shipvault.com/ships/478220</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069962 as AL SIDRIYA</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
@@ -40596,29 +40764,29 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Al Shaheen</t>
+          <t>Al Sidriya</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479144</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478220</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069962 as AL SIDRIYA</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
@@ -40628,29 +40796,29 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>Al Shaheen</t>
+          <t>Al Sidriya</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SIDRIYA/1069962/1</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069962 as AL SIDRIYA</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
@@ -40660,12 +40828,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Lekhraib</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/479151</t>
+          <t>https://www.shipvault.com/ships/479139</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -40675,14 +40843,14 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070727 as LEKHRAIB (MMSI 477262100)</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
@@ -40692,12 +40860,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>Al Nouf</t>
+          <t>Lekhraib</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479139</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -40707,14 +40875,14 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070727 as LEKHRAIB (MMSI 477262100)</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
@@ -40724,29 +40892,29 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Izghawa</t>
+          <t>Lekhraib</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478320</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LEKHRAIB/1070727/477262100</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2694 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070727 as LEKHRAIB (MMSI 477262100)</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
@@ -40756,29 +40924,29 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>Izghawa</t>
+          <t>Ain Snan</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+          <t>https://www.shipvault.com/ships/478221</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069974 as AIN SNAN</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
@@ -40788,29 +40956,29 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Al Wa'ab</t>
+          <t>Ain Snan</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/478321</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478221</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069974 as AIN SNAN</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
@@ -40820,29 +40988,29 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>Al Wa'ab</t>
+          <t>Ain Snan</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AIN-SNAN/1069974/1</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F451" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named</t>
+          <t>placeholder 'Hull 2695 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069974 as AIN SNAN</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
@@ -40852,29 +41020,29 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Prime Glory</t>
+          <t>Al Wasmi</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
+          <t>https://www.shipvault.com/ships/478222</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_clearance))</t>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
         </is>
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>placeholder 'Dalian No 1 G175K-11' -&gt; vessel named; marinetraffic.org lists IMO 1069194 as PRIME GLORY; shipvault still carries a hull placeholder - single source</t>
+          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069986 as AL WASMI</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
@@ -40884,29 +41052,29 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>Friendship Venture</t>
+          <t>Al Wasmi</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>https://www.shipvault.com/ships/469427</t>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478222</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+          <t>PASS (OK (shipvault_api))</t>
         </is>
       </c>
       <c r="F453" s="2" t="inlineStr">
         <is>
-          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069986 as AL WASMI</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>142</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
@@ -40916,52 +41084,660 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Friendship Venture</t>
+          <t>Al Wasmi</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427</t>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-WASMI/1069986/1</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
         <is>
-          <t>PASS (OK (shipvault_api))</t>
+          <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+          <t>placeholder 'Hull 2696 (Hanwha)' -&gt; vessel named; marinetraffic.org independently lists IMO 1069986 as AL WASMI</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479141</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070739 as WADI AL ASKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479141</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070739 as WADI AL ASKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>Wadi Al Askar</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/WADI-AL-ASKAR/1070739/1</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2696 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070739 as WADI AL ASKAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479144</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070741 as AL SHAHEEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479144</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070741 as AL SHAHEEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>Al Shaheen</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-SHAHEEN/1070741/1</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2699 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070741 as AL SHAHEEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>Libsayer</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/LIBSAYER/1070806/1</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2702 (SHI)' -&gt; vessel named; marinetraffic.org lists IMO 1070806 as LIBSAYER; shipvault still carries a hull placeholder - single source</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/479151</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070820 as AL NOUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/479151</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070820 as AL NOUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>Al Nouf</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-NOUF/1070820/1</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 2706 (SHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1070820 as AL NOUF</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478320</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049091 as IZGHAWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478320</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049091 as IZGHAWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>Izghawa</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/IZGHAWA/1049091/1</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3491 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049091 as IZGHAWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/478321</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049118 as AL WA'AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/478321</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049118 as AL WA'AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>Al Wa'ab</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/AL-WA'AB/1049118/1</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Hull 3492 (HDHHI)' -&gt; vessel named; marinetraffic.org independently lists IMO 1049118 as AL WA'AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>Prime Glory</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/PRIME-GLORY/1069194/1</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_clearance))</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>placeholder 'Dalian No 1 G175K-11' -&gt; vessel named; marinetraffic.org lists IMO 1069194 as PRIME GLORY; shipvault still carries a hull placeholder - single source</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="B455" s="2" t="inlineStr">
+      <c r="B472" s="2" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C455" s="2" t="inlineStr">
+      <c r="C472" s="2" t="inlineStr">
         <is>
           <t>Friendship Venture</t>
         </is>
       </c>
-      <c r="D455" s="2" t="inlineStr">
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shipvault.com/ships/469427</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (cf_impersonate, shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>https://shipvaultapi-gjb8c.ondigitalocean.app/api/units/469427</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>PASS (OK (shipvault_api))</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Friendship Venture</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
         <is>
           <t>https://www.marinetraffic.org/ship-owner-manager-ism-data/FRIENDSHIP-VENTURE/1030557/636025371</t>
         </is>
       </c>
-      <c r="E455" s="2" t="inlineStr">
+      <c r="E474" s="2" t="inlineStr">
         <is>
           <t>PASS (OK (cf_clearance))</t>
         </is>
       </c>
-      <c r="F455" s="2" t="inlineStr">
+      <c r="F474" s="2" t="inlineStr">
         <is>
           <t>backend 'Dalian No 1 G175K-12' differs from registry name; marinetraffic.org independently lists IMO 1030557 as FRIENDSHIP VENTURE (MMSI 636025371)</t>
         </is>
